--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E ARCHERY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK BULL L.E ARCHERY.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -652,8 +657,17 @@
           <t>76.9</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>12.8</t>
         </is>
@@ -721,8 +735,17 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -794,8 +817,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -867,8 +899,17 @@
           <t>40</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>9.9</t>
         </is>
@@ -940,8 +981,17 @@
           <t>30.4</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>13.9</t>
         </is>
@@ -1013,8 +1063,17 @@
           <t>31.8</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1086,8 +1145,17 @@
           <t>41.5</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
@@ -1159,8 +1227,17 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1232,8 +1309,17 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
@@ -1305,8 +1391,17 @@
           <t>37.5</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
@@ -1378,8 +1473,17 @@
           <t>38.9</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>15.1</t>
         </is>
@@ -1451,8 +1555,17 @@
           <t>33.3</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>13.1</t>
         </is>
@@ -1524,8 +1637,17 @@
           <t>55.2</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>15.1</t>
         </is>
@@ -1597,8 +1719,17 @@
           <t>28</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>13.1</t>
         </is>
@@ -1670,8 +1801,17 @@
           <t>25.4</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
@@ -1731,8 +1871,17 @@
       </c>
       <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>13.7</t>
         </is>
@@ -1804,8 +1953,17 @@
           <t>37.5</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>12.9</t>
         </is>
@@ -1877,8 +2035,17 @@
           <t>22.2</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
@@ -1950,8 +2117,17 @@
           <t>42.1</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>12.9</t>
         </is>
@@ -2023,8 +2199,17 @@
           <t>61.5</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>10.9</t>
         </is>
@@ -2096,8 +2281,17 @@
           <t>59.3</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
@@ -2169,8 +2363,17 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
@@ -2242,8 +2445,17 @@
           <t>72.2</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -2315,8 +2527,17 @@
           <t>78.6</t>
         </is>
       </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -2388,8 +2609,17 @@
           <t>50</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>14.2</t>
         </is>
@@ -2461,8 +2691,17 @@
           <t>44.2</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>12.7</t>
         </is>
@@ -2534,8 +2773,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -2607,8 +2855,17 @@
           <t>43.5</t>
         </is>
       </c>
-      <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>12.6</t>
         </is>
@@ -2680,8 +2937,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>10.6</t>
         </is>
@@ -2745,8 +3011,17 @@
       </c>
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -2818,8 +3093,17 @@
           <t>25</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -2891,8 +3175,17 @@
           <t>10</t>
         </is>
       </c>
-      <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -2964,8 +3257,17 @@
           <t>24</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>15.3</t>
         </is>
@@ -3037,8 +3339,17 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -3110,8 +3421,17 @@
           <t>14.3</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -3175,8 +3495,17 @@
       </c>
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
         <is>
           <t>8.7</t>
         </is>
@@ -3248,8 +3577,17 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>10.2</t>
         </is>
@@ -3321,8 +3659,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr">
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -3394,8 +3741,17 @@
           <t>60</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -3467,8 +3823,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr">
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -3540,8 +3905,17 @@
           <t>25</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>9.4</t>
         </is>
@@ -3613,8 +3987,17 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr">
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3686,8 +4069,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -3759,8 +4151,17 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr">
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -3832,8 +4233,17 @@
           <t>12.5</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
@@ -3906,7 +4316,8 @@
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr"/>
-      <c r="O47" s="3" t="inlineStr">
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
